--- a/Task-1.xlsx
+++ b/Task-1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\demo\excel_task\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\excel_task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C793AD08-1E57-49DC-A256-1A988B9A73D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC14E0C-7CF3-491D-BE83-E00A360F9D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Task-1" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -642,14 +640,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="5" width="14" customWidth="1"/>
     <col min="6" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -661,7 +659,7 @@
       <c r="G1" s="12"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -673,12 +671,12 @@
       <c r="G2" s="9"/>
       <c r="H2" s="9"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -690,7 +688,7 @@
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
     </row>
-    <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -716,7 +714,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -739,7 +737,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -749,18 +747,20 @@
       <c r="C7" s="2">
         <v>98</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2">
+        <v>100</v>
+      </c>
       <c r="E7" s="2">
         <v>87</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" ref="F7:F15" si="0">SUM(C7:E7)</f>
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -781,7 +781,7 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -804,7 +804,7 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -827,7 +827,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -850,7 +850,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -873,7 +873,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -894,7 +894,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -915,7 +915,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
@@ -936,7 +936,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>31</v>
       </c>
@@ -948,7 +948,7 @@
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -965,7 +965,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -974,7 +974,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -983,7 +983,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>36</v>
       </c>
@@ -992,7 +992,7 @@
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -1001,7 +1001,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -1010,7 +1010,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -1019,7 +1019,7 @@
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1028,7 +1028,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>41</v>
       </c>
@@ -1040,7 +1040,7 @@
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -1048,7 +1048,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>43</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C32" s="6"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C33" s="6"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>48</v>
       </c>
